--- a/product-definitions/spreadsheet/co2-concentration.xlsx
+++ b/product-definitions/spreadsheet/co2-concentration.xlsx
@@ -1950,7 +1950,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>19</v>
@@ -1965,7 +1965,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
         <v>20</v>
@@ -1980,7 +1980,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
         <v>22</v>
@@ -1995,7 +1995,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
         <v>23</v>
@@ -2010,7 +2010,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>25</v>
@@ -2025,7 +2025,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="8" t="s">
         <v>26</v>
@@ -2040,7 +2040,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
         <v>28</v>
@@ -2055,7 +2055,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="17" t="s">
         <v>30</v>
@@ -2070,7 +2070,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="9"/>
@@ -2081,7 +2081,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -2109,7 +2109,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
         <v>12</v>
@@ -2124,7 +2124,7 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
         <v>2</v>
@@ -2139,7 +2139,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
         <v>19</v>
@@ -2154,7 +2154,7 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
         <v>20</v>
@@ -2169,7 +2169,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
         <v>22</v>
@@ -2184,7 +2184,7 @@
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
         <v>23</v>
@@ -2199,7 +2199,7 @@
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>25</v>
@@ -2214,7 +2214,7 @@
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
         <v>26</v>
@@ -2229,7 +2229,7 @@
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7" t="s">
         <v>28</v>
@@ -2244,7 +2244,7 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="17" t="s">
         <v>30</v>
@@ -2259,7 +2259,7 @@
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2270,7 +2270,7 @@
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>38</v>
       </c>
@@ -2283,7 +2283,7 @@
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="7" t="s">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="7" t="s">
         <v>12</v>
@@ -2313,7 +2313,7 @@
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8" t="s">
         <v>2</v>
@@ -2328,7 +2328,7 @@
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
         <v>19</v>
@@ -2343,7 +2343,7 @@
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="7" t="s">
         <v>20</v>
@@ -2358,7 +2358,7 @@
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="7" t="s">
         <v>22</v>
@@ -2373,7 +2373,7 @@
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>23</v>
@@ -2388,7 +2388,7 @@
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
         <v>25</v>
@@ -2403,7 +2403,7 @@
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="8" t="s">
         <v>26</v>
@@ -2418,7 +2418,7 @@
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="7" t="s">
         <v>28</v>
@@ -2433,7 +2433,7 @@
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="17" t="s">
         <v>30</v>
@@ -2448,7 +2448,7 @@
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -2459,14 +2459,14 @@
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="22"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>12</v>
@@ -2484,7 +2484,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>2</v>
@@ -2493,14 +2493,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="22"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>20</v>
@@ -2509,7 +2509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="7" t="s">
         <v>44</v>
@@ -2518,7 +2518,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="9" t="s">
         <v>46</v>
